--- a/Dashboard de Vendas - EShop Paulo Fiuza.xlsx
+++ b/Dashboard de Vendas - EShop Paulo Fiuza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo\Documents\Exercícios de Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D542F524-2EA2-4DA2-9CE0-586FBA46CFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01120BEE-F3AE-445B-93EF-8AD71694B317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,24 @@
     <sheet name="Cálculos" sheetId="2" r:id="rId2"/>
     <sheet name="Dashboard" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="SegmentaçãodeDados_Canal_Venda">#N/A</definedName>
+    <definedName name="SegmentaçãodeDados_Status_Entrega">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId5"/>
+        <x14:slicerCache r:id="rId6"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -33,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="52">
   <si>
     <t>ID_Pedido</t>
   </si>
@@ -188,9 +201,6 @@
     <t>ago</t>
   </si>
   <si>
-    <t>set</t>
-  </si>
-  <si>
     <t>Soma de Quantidade</t>
   </si>
 </sst>
@@ -198,6 +208,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -227,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -235,6 +248,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -270,7 +284,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Novo(a) Planilha do Microsoft Excel.xlsx]Cálculos!Tabela dinâmica1</c:name>
+    <c:name>[Dashboard de Vendas - EShop Paulo Fiuza.xlsx]Cálculos!Tabela dinâmica1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -526,16 +540,16 @@
             <c:numRef>
               <c:f>Cálculos!$B$4:$B$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>"R$"\ #,##0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>32993</c:v>
+                  <c:v>6272</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>67203.5</c:v>
+                  <c:v>19896</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77364</c:v>
+                  <c:v>9474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -630,7 +644,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;R$&quot;\ #,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -646,12 +660,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="700" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -752,7 +763,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -778,7 +788,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Novo(a) Planilha do Microsoft Excel.xlsx]Cálculos!Tabela dinâmica3</c:name>
+    <c:name>[Dashboard de Vendas - EShop Paulo Fiuza.xlsx]Cálculos!Tabela dinâmica3</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -1032,9 +1042,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Cálculos!$E$4:$E$13</c:f>
+              <c:f>Cálculos!$E$4:$E$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>jan</c:v>
                 </c:pt>
@@ -1059,44 +1069,38 @@
                 <c:pt idx="7">
                   <c:v>ago</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>set</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cálculos!$F$4:$F$13</c:f>
+              <c:f>Cálculos!$F$4:$F$12</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:formatCode>"R$"\ #,##0.00</c:formatCode>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>18858</c:v>
+                  <c:v>3640</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18267.5</c:v>
+                  <c:v>3930</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24915</c:v>
+                  <c:v>4960</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17699</c:v>
+                  <c:v>3792</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25486.5</c:v>
+                  <c:v>3760</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19223</c:v>
+                  <c:v>4900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21827.5</c:v>
+                  <c:v>4312</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22524</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8760</c:v>
+                  <c:v>6348</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1192,7 +1196,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;R$&quot;\ #,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1340,7 +1344,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Novo(a) Planilha do Microsoft Excel.xlsx]Cálculos!Tabela dinâmica4</c:name>
+    <c:name>[Dashboard de Vendas - EShop Paulo Fiuza.xlsx]Cálculos!Tabela dinâmica4</c:name>
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
@@ -1839,19 +1843,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>165</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>171</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>137</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>151</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>114</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3638,15 +3642,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
+      <xdr:colOff>57149</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3675,16 +3679,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3713,14 +3717,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
     </xdr:to>
@@ -3747,6 +3751,162 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Canal_Venda">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806CBD80-5814-4780-831C-1FD44C54305D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Canal_Venda"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9848849" y="4695825"/>
+              <a:ext cx="3000375" cy="1257300"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Status_Entrega">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C148F8B-3B23-48F0-B63F-7F2DE0B784C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Status_Entrega"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6543675" y="4695825"/>
+              <a:ext cx="2933700" cy="1276350"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4273,10 +4433,18 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Canal_Venda" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Online"/>
+        <s v="Loja Física"/>
+        <s v="Marketplace"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Status_Entrega" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Entregue"/>
+        <s v="Em trânsito"/>
+        <s v="Cancelado"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Meses" numFmtId="0" databaseField="0">
       <fieldGroup base="1">
@@ -4302,7 +4470,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="1724378371"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -4321,8 +4489,8 @@
     <s v="0.05"/>
     <n v="3800"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1002"/>
@@ -4335,8 +4503,8 @@
     <s v="0.00"/>
     <n v="3000"/>
     <x v="1"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1003"/>
@@ -4349,8 +4517,8 @@
     <s v="0.10"/>
     <n v="1080"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1004"/>
@@ -4363,8 +4531,8 @@
     <s v="0.00"/>
     <n v="750"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1005"/>
@@ -4377,8 +4545,8 @@
     <s v="0.05"/>
     <n v="380"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Cancelado"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1006"/>
@@ -4391,8 +4559,8 @@
     <s v="0.00"/>
     <n v="640"/>
     <x v="4"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1007"/>
@@ -4405,8 +4573,8 @@
     <s v="0.00"/>
     <n v="800"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1008"/>
@@ -4419,8 +4587,8 @@
     <s v="0.08"/>
     <n v="5520"/>
     <x v="2"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1009"/>
@@ -4433,8 +4601,8 @@
     <s v="0.12"/>
     <n v="528"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1010"/>
@@ -4447,8 +4615,8 @@
     <s v="0.00"/>
     <n v="500"/>
     <x v="1"/>
-    <s v="Loja Física"/>
-    <s v="Em trânsito"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1011"/>
@@ -4461,8 +4629,8 @@
     <s v="0.05"/>
     <n v="1140"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1012"/>
@@ -4475,8 +4643,8 @@
     <s v="0.00"/>
     <n v="720"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1013"/>
@@ -4489,8 +4657,8 @@
     <s v="0.05"/>
     <n v="2280"/>
     <x v="0"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1014"/>
@@ -4503,8 +4671,8 @@
     <s v="0.00"/>
     <n v="1500"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Cancelado"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1015"/>
@@ -4517,8 +4685,8 @@
     <s v="0.10"/>
     <n v="2160"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1016"/>
@@ -4531,8 +4699,8 @@
     <s v="0.05"/>
     <n v="1187.5"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1017"/>
@@ -4545,8 +4713,8 @@
     <s v="0.00"/>
     <n v="800"/>
     <x v="4"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1018"/>
@@ -4559,8 +4727,8 @@
     <s v="0.00"/>
     <n v="480"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1019"/>
@@ -4573,8 +4741,8 @@
     <s v="0.05"/>
     <n v="1520"/>
     <x v="1"/>
-    <s v="Marketplace"/>
-    <s v="Em trânsito"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1020"/>
@@ -4587,8 +4755,8 @@
     <s v="0.10"/>
     <n v="4050"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1021"/>
@@ -4601,8 +4769,8 @@
     <s v="0.15"/>
     <n v="850"/>
     <x v="3"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1022"/>
@@ -4615,8 +4783,8 @@
     <s v="0.00"/>
     <n v="1000"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1023"/>
@@ -4629,8 +4797,8 @@
     <s v="0.08"/>
     <n v="1840"/>
     <x v="0"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1024"/>
@@ -4643,8 +4811,8 @@
     <s v="0.00"/>
     <n v="600"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Cancelado"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1025"/>
@@ -4657,8 +4825,8 @@
     <s v="0.05"/>
     <n v="4560"/>
     <x v="2"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1026"/>
@@ -4671,8 +4839,8 @@
     <s v="0.00"/>
     <n v="3000"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1027"/>
@@ -4685,8 +4853,8 @@
     <s v="0.10"/>
     <n v="1512"/>
     <x v="4"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1028"/>
@@ -4699,8 +4867,8 @@
     <s v="0.00"/>
     <n v="750"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1029"/>
@@ -4713,8 +4881,8 @@
     <s v="0.00"/>
     <n v="400"/>
     <x v="1"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1030"/>
@@ -4727,8 +4895,8 @@
     <s v="0.05"/>
     <n v="836"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1031"/>
@@ -4741,8 +4909,8 @@
     <s v="0.05"/>
     <n v="3040"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1032"/>
@@ -4755,8 +4923,8 @@
     <s v="0.12"/>
     <n v="6600"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1033"/>
@@ -4769,8 +4937,8 @@
     <s v="0.15"/>
     <n v="1020"/>
     <x v="0"/>
-    <s v="Loja Física"/>
-    <s v="Cancelado"/>
+    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1034"/>
@@ -4783,8 +4951,8 @@
     <s v="0.05"/>
     <n v="1425"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1035"/>
@@ -4797,8 +4965,8 @@
     <s v="0.00"/>
     <n v="800"/>
     <x v="2"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1036"/>
@@ -4811,8 +4979,8 @@
     <s v="0.10"/>
     <n v="972"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1037"/>
@@ -4825,8 +4993,8 @@
     <s v="0.00"/>
     <n v="1600"/>
     <x v="4"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1038"/>
@@ -4839,8 +5007,8 @@
     <s v="0.00"/>
     <n v="1500"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1039"/>
@@ -4853,8 +5021,8 @@
     <s v="0.05"/>
     <n v="912"/>
     <x v="1"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1040"/>
@@ -4867,8 +5035,8 @@
     <s v="0.00"/>
     <n v="1000"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1041"/>
@@ -4881,8 +5049,8 @@
     <s v="0.08"/>
     <n v="1472"/>
     <x v="3"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1042"/>
@@ -4895,8 +5063,8 @@
     <s v="0.00"/>
     <n v="400"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1043"/>
@@ -4909,8 +5077,8 @@
     <s v="0.05"/>
     <n v="3800"/>
     <x v="0"/>
-    <s v="Marketplace"/>
-    <s v="Cancelado"/>
+    <x v="2"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1044"/>
@@ -4923,8 +5091,8 @@
     <s v="0.10"/>
     <n v="4050"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1045"/>
@@ -4937,8 +5105,8 @@
     <s v="0.10"/>
     <n v="720"/>
     <x v="2"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1046"/>
@@ -4951,8 +5119,8 @@
     <s v="0.00"/>
     <n v="250"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1047"/>
@@ -4965,8 +5133,8 @@
     <s v="0.05"/>
     <n v="1140"/>
     <x v="4"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1048"/>
@@ -4979,8 +5147,8 @@
     <s v="0.05"/>
     <n v="855"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1049"/>
@@ -4993,8 +5161,8 @@
     <s v="0.00"/>
     <n v="2400"/>
     <x v="1"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1050"/>
@@ -5007,8 +5175,8 @@
     <s v="0.05"/>
     <n v="2850"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1051"/>
@@ -5021,8 +5189,8 @@
     <s v="0.10"/>
     <n v="1296"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1052"/>
@@ -5035,8 +5203,8 @@
     <s v="0.05"/>
     <n v="1662.5"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1053"/>
@@ -5049,8 +5217,8 @@
     <s v="0.00"/>
     <n v="800"/>
     <x v="0"/>
-    <s v="Loja Física"/>
-    <s v="Cancelado"/>
+    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1054"/>
@@ -5063,8 +5231,8 @@
     <s v="0.00"/>
     <n v="720"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1055"/>
@@ -5077,8 +5245,8 @@
     <s v="0.10"/>
     <n v="5040"/>
     <x v="2"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1056"/>
@@ -5091,8 +5259,8 @@
     <s v="0.08"/>
     <n v="5520"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1057"/>
@@ -5105,8 +5273,8 @@
     <s v="0.15"/>
     <n v="1360"/>
     <x v="4"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1058"/>
@@ -5119,8 +5287,8 @@
     <s v="0.00"/>
     <n v="750"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1059"/>
@@ -5133,8 +5301,8 @@
     <s v="0.05"/>
     <n v="1900"/>
     <x v="1"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1060"/>
@@ -5147,8 +5315,8 @@
     <s v="0.10"/>
     <n v="1188"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1061"/>
@@ -5161,8 +5329,8 @@
     <s v="0.05"/>
     <n v="3040"/>
     <x v="3"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1062"/>
@@ -5175,8 +5343,8 @@
     <s v="0.00"/>
     <n v="1500"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1063"/>
@@ -5189,8 +5357,8 @@
     <s v="0.10"/>
     <n v="1728"/>
     <x v="0"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1064"/>
@@ -5203,8 +5371,8 @@
     <s v="0.00"/>
     <n v="500"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Cancelado"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1065"/>
@@ -5217,8 +5385,8 @@
     <s v="0.05"/>
     <n v="1140"/>
     <x v="2"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1066"/>
@@ -5231,8 +5399,8 @@
     <s v="0.00"/>
     <n v="320"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1067"/>
@@ -5245,8 +5413,8 @@
     <s v="0.05"/>
     <n v="3800"/>
     <x v="4"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1068"/>
@@ -5259,8 +5427,8 @@
     <s v="0.10"/>
     <n v="4050"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1069"/>
@@ -5273,8 +5441,8 @@
     <s v="0.00"/>
     <n v="720"/>
     <x v="1"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1070"/>
@@ -5287,8 +5455,8 @@
     <s v="0.05"/>
     <n v="1425"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1071"/>
@@ -5301,8 +5469,8 @@
     <s v="0.00"/>
     <n v="400"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1072"/>
@@ -5315,8 +5483,8 @@
     <s v="0.00"/>
     <n v="600"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1073"/>
@@ -5329,8 +5497,8 @@
     <s v="0.00"/>
     <n v="1600"/>
     <x v="0"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1074"/>
@@ -5343,8 +5511,8 @@
     <s v="0.05"/>
     <n v="2850"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Cancelado"/>
+    <x v="0"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1075"/>
@@ -5357,8 +5525,8 @@
     <s v="0.12"/>
     <n v="2640"/>
     <x v="2"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1076"/>
@@ -5371,8 +5539,8 @@
     <s v="0.00"/>
     <n v="1000"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1077"/>
@@ -5385,8 +5553,8 @@
     <s v="0.05"/>
     <n v="1522"/>
     <x v="4"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1078"/>
@@ -5399,8 +5567,8 @@
     <s v="0.00"/>
     <n v="560"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1079"/>
@@ -5413,8 +5581,8 @@
     <s v="0.05"/>
     <n v="2280"/>
     <x v="1"/>
-    <s v="Marketplace"/>
-    <s v="Em trânsito"/>
+    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1080"/>
@@ -5427,8 +5595,8 @@
     <s v="0.10"/>
     <n v="5400"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1081"/>
@@ -5441,8 +5609,8 @@
     <s v="0.15"/>
     <n v="1190"/>
     <x v="3"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1082"/>
@@ -5455,8 +5623,8 @@
     <s v="0.05"/>
     <n v="1187.5"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1083"/>
@@ -5469,8 +5637,8 @@
     <s v="0.00"/>
     <n v="800"/>
     <x v="0"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1084"/>
@@ -5483,8 +5651,8 @@
     <s v="0.05"/>
     <n v="798"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1085"/>
@@ -5497,8 +5665,8 @@
     <s v="0.08"/>
     <n v="4416"/>
     <x v="2"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1086"/>
@@ -5511,8 +5679,8 @@
     <s v="0.00"/>
     <n v="3000"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1087"/>
@@ -5525,8 +5693,8 @@
     <s v="0.10"/>
     <n v="1296"/>
     <x v="4"/>
-    <s v="Marketplace"/>
-    <s v="Cancelado"/>
+    <x v="2"/>
+    <x v="2"/>
   </r>
   <r>
     <n v="1088"/>
@@ -5539,8 +5707,8 @@
     <s v="0.00"/>
     <n v="750"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Em trânsito"/>
+    <x v="0"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1089"/>
@@ -5553,8 +5721,8 @@
     <s v="0.05"/>
     <n v="1140"/>
     <x v="1"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1090"/>
@@ -5567,8 +5735,8 @@
     <s v="0.00"/>
     <n v="800"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1091"/>
@@ -5581,8 +5749,8 @@
     <s v="0.05"/>
     <n v="3800"/>
     <x v="3"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1092"/>
@@ -5595,8 +5763,8 @@
     <s v="0.10"/>
     <n v="4050"/>
     <x v="4"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1093"/>
@@ -5609,8 +5777,8 @@
     <s v="0.10"/>
     <n v="792"/>
     <x v="0"/>
-    <s v="Loja Física"/>
-    <s v="Entregue"/>
+    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1094"/>
@@ -5623,8 +5791,8 @@
     <s v="0.00"/>
     <n v="1000"/>
     <x v="1"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1095"/>
@@ -5637,8 +5805,8 @@
     <s v="0.00"/>
     <n v="400"/>
     <x v="2"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1096"/>
@@ -5651,8 +5819,8 @@
     <s v="0.10"/>
     <n v="1080"/>
     <x v="3"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1097"/>
@@ -5665,8 +5833,8 @@
     <s v="0.05"/>
     <n v="3040"/>
     <x v="4"/>
-    <s v="Loja Física"/>
-    <s v="Em trânsito"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
   <r>
     <n v="1098"/>
@@ -5679,8 +5847,8 @@
     <s v="0.05"/>
     <n v="2850"/>
     <x v="0"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1099"/>
@@ -5693,8 +5861,8 @@
     <s v="0.10"/>
     <n v="1620"/>
     <x v="1"/>
-    <s v="Marketplace"/>
-    <s v="Entregue"/>
+    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <n v="1100"/>
@@ -5707,14 +5875,14 @@
     <s v="0.00"/>
     <n v="1250"/>
     <x v="2"/>
-    <s v="Online"/>
-    <s v="Entregue"/>
+    <x v="0"/>
+    <x v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58F77A8D-C748-48ED-8248-2757B69E77EE}" name="Tabela dinâmica4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58F77A8D-C748-48ED-8248-2757B69E77EE}" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="I3:J9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -5736,8 +5904,22 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -5991,8 +6173,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1FA91DC-88D7-485E-A4D0-D5B2B9D22B92}" name="Tabela dinâmica3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="E3:F13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1FA91DC-88D7-485E-A4D0-D5B2B9D22B92}" name="Tabela dinâmica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="E3:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -6376,8 +6558,22 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="15">
         <item sd="0" x="0"/>
@@ -6402,7 +6598,7 @@
     <field x="12"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="10">
+  <rowItems count="9">
     <i>
       <x v="1"/>
     </i>
@@ -6427,9 +6623,6 @@
     <i>
       <x v="8"/>
     </i>
-    <i>
-      <x v="9"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -6438,7 +6631,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Soma de Receita_Liquida" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Soma de Receita_Liquida" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
@@ -6491,7 +6684,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E638EF7A-FE42-4AEC-B6DF-7410710C1ACC}" name="Tabela dinâmica1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E638EF7A-FE42-4AEC-B6DF-7410710C1ACC}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -6883,8 +7076,22 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="15">
         <item x="0"/>
@@ -6926,7 +7133,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Soma de Receita_Liquida" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Soma de Receita_Liquida" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
@@ -6958,6 +7165,51 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Canal_Venda" xr10:uid="{6591769F-2D59-4D05-BEF2-F4A6E5024B8F}" sourceName="Canal_Venda">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica1"/>
+    <pivotTable tabId="2" name="Tabela dinâmica3"/>
+    <pivotTable tabId="2" name="Tabela dinâmica4"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1724378371">
+      <items count="3">
+        <i x="1" s="1"/>
+        <i x="2"/>
+        <i x="0"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Status_Entrega" xr10:uid="{7A29B554-B19C-4D8F-8E9D-AEADC89A4F8A}" sourceName="Status_Entrega">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica1"/>
+    <pivotTable tabId="2" name="Tabela dinâmica3"/>
+    <pivotTable tabId="2" name="Tabela dinâmica4"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1724378371">
+      <items count="3">
+        <i x="2"/>
+        <i x="1"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Canal_Venda" xr10:uid="{D219DF8A-9F52-486D-8A7C-0CD478977844}" cache="SegmentaçãodeDados_Canal_Venda" caption="Canal_Venda" rowHeight="241300"/>
+  <slicer name="Status_Entrega" xr10:uid="{635DA046-A217-4456-A65D-7FEA287AF4F2}" cache="SegmentaçãodeDados_Status_Entrega" caption="Status_Entrega" rowHeight="241300"/>
+</slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11106,7 +11358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E61BF8D-4A5C-490C-845D-2935AD7BAFFB}">
-  <dimension ref="A3:J13"/>
+  <dimension ref="A3:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -11134,151 +11386,144 @@
         <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="4">
-        <v>32993</v>
+      <c r="B4" s="5">
+        <v>6272</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="4">
-        <v>18858</v>
+      <c r="F4" s="5">
+        <v>3640</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="J4" s="4">
-        <v>165</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
-        <v>67203.5</v>
+      <c r="B5" s="5">
+        <v>19896</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="4">
-        <v>18267.5</v>
+      <c r="F5" s="5">
+        <v>3930</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="4">
-        <v>171</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4">
-        <v>77364</v>
+      <c r="B6" s="5">
+        <v>9474</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="4">
-        <v>24915</v>
+      <c r="F6" s="5">
+        <v>4960</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J6" s="4">
-        <v>137</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="4">
-        <v>177560.5</v>
+      <c r="B7" s="5">
+        <v>35642</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="4">
-        <v>17699</v>
+      <c r="F7" s="5">
+        <v>3792</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J7" s="4">
-        <v>151</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="4">
-        <v>25486.5</v>
+      <c r="F8" s="5">
+        <v>3760</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="4">
-        <v>114</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="4">
-        <v>19223</v>
+      <c r="F9" s="5">
+        <v>4900</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="4">
-        <v>738</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="4">
-        <v>21827.5</v>
+      <c r="F10" s="5">
+        <v>4312</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="4">
-        <v>22524</v>
+      <c r="F11" s="5">
+        <v>6348</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="4">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="4">
-        <v>177560.5</v>
+      <c r="F12" s="5">
+        <v>35642</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -11289,5 +11534,12 @@
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Dashboard de Vendas - EShop Paulo Fiuza.xlsx
+++ b/Dashboard de Vendas - EShop Paulo Fiuza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo\Documents\Exercícios de Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01120BEE-F3AE-445B-93EF-8AD71694B317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC9263E-7DBD-479B-BD6D-194813AB433B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="46">
   <si>
     <t>ID_Pedido</t>
   </si>
@@ -177,28 +177,10 @@
     <t>Soma de Receita_Liquida</t>
   </si>
   <si>
-    <t>jan</t>
-  </si>
-  <si>
     <t>fev</t>
   </si>
   <si>
-    <t>mar</t>
-  </si>
-  <si>
-    <t>abr</t>
-  </si>
-  <si>
-    <t>mai</t>
-  </si>
-  <si>
-    <t>jun</t>
-  </si>
-  <si>
     <t>jul</t>
-  </si>
-  <si>
-    <t>ago</t>
   </si>
   <si>
     <t>Soma de Quantidade</t>
@@ -207,7 +189,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
@@ -220,12 +202,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -240,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -249,19 +237,90 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="1" tint="0.34998626667073579"/>
+          <bgColor theme="1" tint="0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Estilo de Segmentação de Dados 1" pivot="0" table="0" count="3" xr9:uid="{0C6100A0-BF6C-4B88-BEB1-5925B713CA4C}">
+      <tableStyleElement type="wholeTable" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="Estilo de Segmentação de Dados 2" pivot="0" table="0" count="1" xr9:uid="{B479B659-F464-4041-8825-E087DF09D84E}">
+      <tableStyleElement type="wholeTable" dxfId="2"/>
+    </tableStyle>
+    <tableStyle name="Estilo de Segmentação de Dados 3" pivot="0" table="0" count="1" xr9:uid="{2700BB0F-09E0-44A4-AEF4-97258F5275B4}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
+      <x14:dxfs count="2">
+        <dxf>
+          <fill>
+            <patternFill>
+              <bgColor theme="4"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill>
+              <bgColor theme="4" tint="0.39994506668294322"/>
+            </patternFill>
+          </fill>
+        </dxf>
+      </x14:dxfs>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="Estilo de Segmentação de Dados 3">
+        <x14:slicerStyle name="Estilo de Segmentação de Dados 1">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="0"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+        <x14:slicerStyle name="Estilo de Segmentação de Dados 2"/>
+        <x14:slicerStyle name="Estilo de Segmentação de Dados 3"/>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -289,6 +348,46 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </a:rPr>
+              <a:t>Faturamento por Produto (R$)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -302,13 +401,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -322,17 +427,118 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="diamond"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -352,121 +558,8 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -510,46 +603,63 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Cálculos!$A$4:$A$7</c:f>
+              <c:f>Cálculos!$A$4:$A$5</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Acessórios</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>Celulares</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Computadores</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cálculos!$B$4:$B$7</c:f>
+              <c:f>Cálculos!$B$4:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>"R$"\ #,##0.00</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>6272</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>19896</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9474</c:v>
+                  <c:v>3800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -568,7 +678,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
         <c:axId val="731303631"/>
         <c:axId val="731311951"/>
       </c:barChart>
@@ -585,11 +696,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -603,9 +714,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -634,9 +744,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -644,7 +754,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="&quot;R$&quot;\ #,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -660,9 +770,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -684,37 +796,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -727,17 +808,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -762,7 +854,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -793,6 +884,54 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </a:rPr>
+              <a:t>Evolução Mensal</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.32102393827277614"/>
+          <c:y val="4.8683914510686162E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -806,13 +945,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -826,20 +971,95 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
+          <a:ln w="34925" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -859,124 +1079,8 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -1029,78 +1133,90 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Cálculos!$E$4:$E$12</c:f>
+              <c:f>Cálculos!$E$4:$E$6</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>jan</c:v>
+                  <c:v>fev</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>fev</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>mar</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>abr</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>mai</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>jun</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>jul</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>ago</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cálculos!$F$4:$F$12</c:f>
+              <c:f>Cálculos!$F$4:$F$6</c:f>
               <c:numCache>
                 <c:formatCode>"R$"\ #,##0.00</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>3640</c:v>
+                  <c:v>1520</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3930</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4960</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3792</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3760</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4900</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4312</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6348</c:v>
+                  <c:v>2280</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1120,6 +1236,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="810203823"/>
         <c:axId val="810212975"/>
@@ -1139,9 +1256,9 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="10000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1155,9 +1272,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1186,9 +1302,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1214,9 +1330,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1239,37 +1354,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -1282,17 +1366,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -1317,8 +1412,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -1349,6 +1442,54 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </a:rPr>
+              <a:t>Desempenho por Região</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.24970846835000496"/>
+          <c:y val="3.335053203819608E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1362,13 +1503,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -1382,19 +1529,92 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1414,195 +1634,8 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -1626,77 +1659,70 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="8"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="9"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="10"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="11"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="12"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16152345767912213"/>
+          <c:y val="0.20083391285491023"/>
+          <c:w val="0.51790715027420775"/>
+          <c:h val="0.74218603016503282"/>
+        </c:manualLayout>
+      </c:layout>
       <c:doughnutChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -1717,15 +1743,42 @@
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1737,15 +1790,42 @@
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1757,15 +1837,42 @@
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1777,15 +1884,42 @@
             <c:idx val="3"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1797,15 +1931,42 @@
             <c:idx val="4"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1815,22 +1976,10 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Cálculos!$I$4:$I$9</c:f>
+              <c:f>Cálculos!$I$4:$I$5</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Centro-Oeste</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Nordeste</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Norte</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Sudeste</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Sul</c:v>
                 </c:pt>
               </c:strCache>
@@ -1838,24 +1987,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cálculos!$J$4:$J$9</c:f>
+              <c:f>Cálculos!$J$4:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>27</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1903,9 +2040,8 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1929,17 +2065,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -1965,7 +2112,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -2098,35 +2244,33 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2134,26 +2278,34 @@
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -2162,9 +2314,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2183,14 +2334,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -2199,20 +2342,20 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2221,13 +2364,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2239,10 +2382,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2251,16 +2394,17 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2278,21 +2422,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2311,14 +2452,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2330,14 +2470,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2351,9 +2491,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2367,12 +2506,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -2384,9 +2517,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2401,14 +2534,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2420,14 +2552,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2439,14 +2571,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2455,14 +2586,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2470,7 +2600,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2483,11 +2613,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2495,14 +2635,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2514,12 +2654,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2535,7 +2682,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2544,9 +2690,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2562,14 +2707,13 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2578,9 +2722,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2592,46 +2735,38 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2639,26 +2774,34 @@
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -2667,9 +2810,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2688,14 +2830,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -2704,45 +2838,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2754,31 +2878,29 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -2796,21 +2918,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2820,20 +2939,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2847,14 +2966,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2868,9 +2987,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2884,12 +3002,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -2901,9 +3013,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2918,14 +3030,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2937,14 +3048,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2956,14 +3067,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2972,14 +3082,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2987,7 +3096,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -3000,11 +3109,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -3012,14 +3131,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3031,12 +3150,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3052,7 +3178,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3061,9 +3186,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3073,7 +3197,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -3081,9 +3205,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -3094,9 +3218,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3108,46 +3231,38 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="257">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3155,37 +3270,44 @@
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3204,14 +3326,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -3220,49 +3334,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -3274,10 +3374,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -3286,16 +3386,17 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -3313,21 +3414,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3346,14 +3444,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3365,14 +3462,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -3386,9 +3483,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3402,12 +3498,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -3419,9 +3509,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3436,14 +3526,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -3455,14 +3544,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -3474,14 +3563,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -3490,14 +3578,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -3505,7 +3592,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -3518,11 +3605,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -3530,14 +3627,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3549,12 +3646,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3570,7 +3674,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3579,9 +3682,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3597,14 +3699,13 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3613,9 +3714,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3627,12 +3727,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3642,13 +3736,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
@@ -3679,14 +3773,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>228601</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>95251</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
@@ -3717,16 +3811,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:rowOff>28574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3755,22 +3849,22 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="Canal_Venda">
+            <xdr:cNvPr id="5" name="Canal de Vendas">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806CBD80-5814-4780-831C-1FD44C54305D}"/>
@@ -3785,7 +3879,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Canal_Venda"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Canal de Vendas"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -3800,7 +3894,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9848849" y="4695825"/>
+              <a:off x="6457949" y="4714875"/>
               <a:ext cx="3000375" cy="1257300"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3833,14 +3927,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -3848,7 +3942,7 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Status_Entrega">
+            <xdr:cNvPr id="6" name="Status de Entrega">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C148F8B-3B23-48F0-B63F-7F2DE0B784C7}"/>
@@ -3863,7 +3957,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Status_Entrega"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Status de Entrega"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -3878,7 +3972,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6543675" y="4695825"/>
+              <a:off x="3419475" y="4695825"/>
               <a:ext cx="2933700" cy="1276350"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5882,299 +5976,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58F77A8D-C748-48ED-8248-2757B69E77EE}" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="I3:J9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de Quantidade" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="18">
-    <chartFormat chart="3" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1FA91DC-88D7-485E-A4D0-D5B2B9D22B92}" name="Tabela dinâmica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="E3:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D1FA91DC-88D7-485E-A4D0-D5B2B9D22B92}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="E3:F6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -6560,8 +6363,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="1"/>
-        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
         <item h="1" x="0"/>
         <item t="default"/>
       </items>
@@ -6569,8 +6372,8 @@
     <pivotField showAll="0">
       <items count="4">
         <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -6598,30 +6401,12 @@
     <field x="12"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="9">
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="3">
     <i>
       <x v="2"/>
     </i>
     <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
       <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
     </i>
     <i t="grand">
       <x/>
@@ -6683,9 +6468,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E638EF7A-FE42-4AEC-B6DF-7410710C1ACC}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E638EF7A-FE42-4AEC-B6DF-7410710C1ACC}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -7078,8 +6863,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="1"/>
-        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
         <item h="1" x="0"/>
         <item t="default"/>
       </items>
@@ -7087,8 +6872,8 @@
     <pivotField showAll="0">
       <items count="4">
         <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -7115,15 +6900,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -7167,6 +6946,285 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58F77A8D-C748-48ED-8248-2757B69E77EE}" name="Tabela dinâmica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="I3:J5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de Quantidade" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="18">
+    <chartFormat chart="3" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Canal_Venda" xr10:uid="{6591769F-2D59-4D05-BEF2-F4A6E5024B8F}" sourceName="Canal_Venda">
   <pivotTables>
@@ -7177,8 +7235,8 @@
   <data>
     <tabular pivotCacheId="1724378371">
       <items count="3">
-        <i x="1" s="1"/>
-        <i x="2"/>
+        <i x="1"/>
+        <i x="2" s="1"/>
         <i x="0"/>
       </items>
     </tabular>
@@ -7197,8 +7255,8 @@
     <tabular pivotCacheId="1724378371">
       <items count="3">
         <i x="2"/>
-        <i x="1"/>
-        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0"/>
       </items>
     </tabular>
   </data>
@@ -7207,8 +7265,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Canal_Venda" xr10:uid="{D219DF8A-9F52-486D-8A7C-0CD478977844}" cache="SegmentaçãodeDados_Canal_Venda" caption="Canal_Venda" rowHeight="241300"/>
-  <slicer name="Status_Entrega" xr10:uid="{635DA046-A217-4456-A65D-7FEA287AF4F2}" cache="SegmentaçãodeDados_Status_Entrega" caption="Status_Entrega" rowHeight="241300"/>
+  <slicer name="Canal de Vendas" xr10:uid="{D219DF8A-9F52-486D-8A7C-0CD478977844}" cache="SegmentaçãodeDados_Canal_Venda" caption="Canal de Vendas" style="Estilo de Segmentação de Dados 1" rowHeight="241300"/>
+  <slicer name="Status de Entrega" xr10:uid="{635DA046-A217-4456-A65D-7FEA287AF4F2}" cache="SegmentaçãodeDados_Status_Entrega" caption="Status de Entrega" style="Estilo de Segmentação de Dados 1" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -7217,7 +7275,7 @@
   <autoFilter ref="A1:L101" xr:uid="{E84C2B2F-161E-4C28-9018-4CEEA5BA36AD}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{497BCFE0-483B-4398-A9E5-C8FBF7F11C86}" name="ID_Pedido"/>
-    <tableColumn id="2" xr3:uid="{09EC1995-425B-4509-9A84-9874D23D01D0}" name="Data" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{09EC1995-425B-4509-9A84-9874D23D01D0}" name="Data" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{C9F2D94B-C1A3-4B3D-9975-A7A7349F65FB}" name="Produto"/>
     <tableColumn id="4" xr3:uid="{43768A48-ADDB-4163-9CB5-C28D8973BF12}" name="Categoria"/>
     <tableColumn id="5" xr3:uid="{3C25BD61-486C-4EB2-841F-6B964CF08D4E}" name="Quantidade"/>
@@ -11358,7 +11416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E61BF8D-4A5C-490C-845D-2935AD7BAFFB}">
-  <dimension ref="A3:J12"/>
+  <dimension ref="A3:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -11386,139 +11444,55 @@
         <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5">
-        <v>6272</v>
+        <v>3800</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F4" s="5">
-        <v>3640</v>
+        <v>1520</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J4" s="4">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B5" s="5">
-        <v>19896</v>
+        <v>3800</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F5" s="5">
-        <v>3930</v>
+        <v>2280</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J5" s="4">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5">
-        <v>9474</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F6" s="5">
-        <v>4960</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="4">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="5">
-        <v>35642</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="5">
-        <v>3792</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="5">
-        <v>3760</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="5">
-        <v>4900</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="4">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="5">
-        <v>4312</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="5">
-        <v>6348</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="5">
-        <v>35642</v>
+        <v>3800</v>
       </c>
     </row>
   </sheetData>
@@ -11531,13 +11505,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B9062E-3787-4E44-ADB1-C050CFD844A4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="6"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>
